--- a/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/lda_confusion_matrix.xlsx
+++ b/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/lda_confusion_matrix.xlsx
@@ -463,10 +463,10 @@
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -476,13 +476,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
         <v>4</v>
@@ -495,13 +495,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
         <v>4</v>
@@ -520,10 +520,10 @@
         <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/lda_confusion_matrix.xlsx
+++ b/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/lda_confusion_matrix.xlsx
@@ -457,16 +457,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -476,16 +476,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -495,16 +495,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -517,13 +517,13 @@
         <v>57</v>
       </c>
       <c r="C5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/lda_confusion_matrix.xlsx
+++ b/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/lda_confusion_matrix.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,11 +444,6 @@
           <t>Cluster C2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Cluster C3</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -457,16 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -476,54 +468,29 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
-      </c>
-      <c r="E3" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Cluster C3</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>78</v>
+      </c>
+      <c r="C4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D4" t="n">
         <v>28</v>
-      </c>
-      <c r="C4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E4" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>57</v>
-      </c>
-      <c r="C5" t="n">
-        <v>14</v>
-      </c>
-      <c r="D5" t="n">
-        <v>26</v>
-      </c>
-      <c r="E5" t="n">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
